--- a/data/input/accounting/13375357_032025.xlsx
+++ b/data/input/accounting/13375357_032025.xlsx
@@ -5846,7 +5846,7 @@
     <col min="7" max="7" width="16.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="18.75" thickBot="1">
+    <row r="1" spans="1:7" ht="15" thickBot="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -6058,7 +6058,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="19.5">
+    <row r="11" spans="1:7">
       <c r="A11" s="18">
         <v>4</v>
       </c>
@@ -12155,7 +12155,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="308" spans="1:7" ht="19.5">
+    <row r="308" spans="1:7">
       <c r="A308" s="18">
         <v>14</v>
       </c>
@@ -13752,7 +13752,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="385" spans="1:7" ht="19.5">
+    <row r="385" spans="1:7">
       <c r="A385" s="18">
         <v>21</v>
       </c>
@@ -13942,7 +13942,7 @@
         <v>744</v>
       </c>
     </row>
-    <row r="395" spans="1:7" ht="19.5">
+    <row r="395" spans="1:7">
       <c r="A395" s="18">
         <v>25</v>
       </c>
@@ -14005,7 +14005,7 @@
         <v>750</v>
       </c>
     </row>
-    <row r="398" spans="1:7" ht="19.5">
+    <row r="398" spans="1:7">
       <c r="A398" s="18">
         <v>25</v>
       </c>
@@ -15161,7 +15161,7 @@
         <v>855</v>
       </c>
     </row>
-    <row r="454" spans="1:7" ht="19.5">
+    <row r="454" spans="1:7">
       <c r="A454" s="18">
         <v>28</v>
       </c>
